--- a/Design Files/Dimmer-Board-v1.0/BOM/Client-BOM-Dimmer-Board-v1.0.xlsx
+++ b/Design Files/Dimmer-Board-v1.0/BOM/Client-BOM-Dimmer-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -217,6 +217,30 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Heatsink</t>
+  </si>
+  <si>
+    <t>35*12*25MM 6063-T5 aluminum Heat sink/heatsink</t>
+  </si>
+  <si>
+    <t>35*12*25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XSD </t>
+  </si>
+  <si>
+    <t>Screw</t>
+  </si>
+  <si>
+    <t>phillips small pan head screw and spring pad combination</t>
+  </si>
+  <si>
+    <t>Tong Ming</t>
   </si>
 </sst>
 </file>
@@ -709,7 +733,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -805,7 +829,7 @@
     <row r="4" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B12" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B14" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -1089,6 +1113,68 @@
         <v>1</v>
       </c>
       <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="9">
+        <v>1</v>
+      </c>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="11">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="10">
+        <v>266068</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="9">
+        <v>1</v>
+      </c>
+      <c r="K14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
